--- a/mca31.xlsx
+++ b/mca31.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1785f9ba15486eb2/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A5372BA-47B1-4CF1-BF28-65F241A2D316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{55DC002F-81D9-46D0-A107-9A53E410268D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="107">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -355,6 +355,9 @@
   </si>
   <si>
     <t>Still sick</t>
+  </si>
+  <si>
+    <t>Went to golden temple yesterday</t>
   </si>
 </sst>
 </file>
@@ -3157,27 +3160,51 @@
         <v>105</v>
       </c>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="13"/>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15" t="str">
+    <row r="50" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A50" s="13">
+        <v>46285</v>
+      </c>
+      <c r="B50" s="14">
+        <v>120</v>
+      </c>
+      <c r="C50" s="14">
+        <v>0</v>
+      </c>
+      <c r="D50" s="14">
+        <v>25</v>
+      </c>
+      <c r="E50" s="14">
+        <v>22</v>
+      </c>
+      <c r="F50" s="14">
+        <v>0</v>
+      </c>
+      <c r="G50" s="14">
+        <v>0</v>
+      </c>
+      <c r="H50" s="14">
+        <v>60</v>
+      </c>
+      <c r="I50" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J50" s="15" t="str">
+        <v>227</v>
+      </c>
+      <c r="J50" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K50" s="16"/>
-      <c r="L50" s="16"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="17"/>
+        <v>1213</v>
+      </c>
+      <c r="K50" s="16" t="s">
+        <v>49</v>
+      </c>
+      <c r="L50" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="M50" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="N50" s="17" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A51" s="13"/>

--- a/mca31.xlsx
+++ b/mca31.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1785f9ba15486eb2/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{55DC002F-81D9-46D0-A107-9A53E410268D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{B9F26369-BAC2-478B-8E55-E5794A1CAFBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="108">
   <si>
     <t>My Data, My Code</t>
   </si>
@@ -358,6 +358,9 @@
   </si>
   <si>
     <t>Went to golden temple yesterday</t>
+  </si>
+  <si>
+    <t>Coughing in the class ruined my day</t>
   </si>
 </sst>
 </file>
@@ -3206,27 +3209,51 @@
         <v>106</v>
       </c>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="13"/>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15" t="str">
+    <row r="51" spans="1:14" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="13">
+        <v>46286</v>
+      </c>
+      <c r="B51" s="14">
+        <v>422</v>
+      </c>
+      <c r="C51" s="14">
+        <v>28</v>
+      </c>
+      <c r="D51" s="14">
+        <v>60</v>
+      </c>
+      <c r="E51" s="14">
+        <v>30</v>
+      </c>
+      <c r="F51" s="14">
+        <v>150</v>
+      </c>
+      <c r="G51" s="14">
+        <v>3</v>
+      </c>
+      <c r="H51" s="14">
+        <v>111</v>
+      </c>
+      <c r="I51" s="15">
         <f t="shared" si="0"/>
-        <v/>
-      </c>
-      <c r="J51" s="15" t="str">
+        <v>801</v>
+      </c>
+      <c r="J51" s="15">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-      <c r="K51" s="16"/>
-      <c r="L51" s="16"/>
-      <c r="M51" s="16"/>
-      <c r="N51" s="17"/>
+        <v>639</v>
+      </c>
+      <c r="K51" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="L51" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="M51" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="N51" s="17" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A52" s="13"/>

--- a/mca31.xlsx
+++ b/mca31.xlsx
@@ -2206,7 +2206,7 @@
       </c>
       <c r="N29" s="17" t="inlineStr">
         <is>
-          <t>Good day overall</t>
+          <t>Good day overall, nothing to complain about</t>
         </is>
       </c>
     </row>
